--- a/docs/civicview_financial_model.xlsx
+++ b/docs/civicview_financial_model.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="245">
   <si>
     <t xml:space="preserve">CivicView Financial Model</t>
   </si>
@@ -274,12 +274,66 @@
     <t xml:space="preserve">Misc (legal, accounting templates, etc.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Stripe fees included via subscription processing</t>
+    <t xml:space="preserve">Legal templates, accounting subscriptions, etc. Payment processing fees are broken out in the Payment processing section below.</t>
   </si>
   <si>
     <t xml:space="preserve">Total other recurring (annual)</t>
   </si>
   <si>
+    <t xml:space="preserve">Payment processing — app store + web subscription fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iOS App Store revenue share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of paying subscribers who subscribe via iOS in-app purchase. Default 30% based on civic-app user mix.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Play revenue share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Android in-app purchase share. Default 20% — US civic apps skew slightly iOS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web (Stripe) revenue share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto = 1 - iOS - Android. If this goes negative, your iOS + Android shares sum &gt; 100%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iOS App Store fee rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Small Business Program: 15% if App Store revenue &lt;$1M/yr. Flip to 30% once you cross that threshold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Play fee rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Play also 15% on first $1M/yr per developer; jumps to 30% beyond.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stripe / web processing rate (effective)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stripe 2.9% + $0.30 per transaction. On $5/mo billing the fixed fee dominates (~9% effective); annual billing drops to ~3.5%. 5% is a moderate blend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended payment-processing rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto: weighted average across iOS / Android / Web. The P&amp;L applies this to total subscription revenue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity (external penetration testing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External penetration test (annual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y1 skipped — at 1K users, automated scanning (CodeQL + Dependabot) is sufficient. Y2 ($5K) first external review when revenue + user data justify the spend. Y3-Y5 ramp follows attack-surface growth. Bi-annual cadence past Y5 worth considering.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
@@ -295,6 +349,15 @@
     <t xml:space="preserve">• Cost-per-paying-subscriber at Y5 = ~$32 (mostly ID.me amortized + Render). LTV at $60/yr × 2yr average tenure = $120. Positive margin.</t>
   </si>
   <si>
+    <t xml:space="preserve">• Payment processing assumes a 30/20/50 iOS/Android/Web split. Adjust B40:B41 if your acquisition channel mix differs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• App store fees stay at 15% under the Small Business Program ($1M/yr per store). Flip B43/B44 to 30% if you cross the threshold (~Y5 aggressive ramp).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Penetration testing scales with attack surface. Y1 ($5K) reflects a small footprint; Y5 ($20K) anticipates 500K users + 3 identity types + admin moderation surface.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ID.me verification costs — what would it cost if we hit X users?</t>
   </si>
   <si>
@@ -418,6 +481,9 @@
     <t xml:space="preserve">• Beyond 500K, you should renegotiate Render Enterprise OR plan a cloud migration. The $5K/mo for 1M users is likely a starting point for negotiation, not a ceiling.</t>
   </si>
   <si>
+    <t xml:space="preserve">• Subs-needed (col E) and monthly-net (col H) now use the post-fee effective sub price = $5 × (1 - blended payment rate). At default 30/20/50 iOS/Android/Web mix the blended rate is ~10%, so effective price is $4.50.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Render hosting — configuration at each scale</t>
   </si>
   <si>
@@ -601,6 +667,12 @@
     <t xml:space="preserve">Other recurring infra (annual)</t>
   </si>
   <si>
+    <t xml:space="preserve">Payment processing (app store + Stripe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External penetration test</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total costs</t>
   </si>
   <si>
@@ -619,19 +691,25 @@
     <t xml:space="preserve">Reading this sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">• Y1 shows a small loss because ID.me verification + initial Render costs exceed early subscription revenue at 1K users.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Y2 hits break-even and stays profitable through Y5 under your moderate ramp + 3% conversion assumptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Cumulative net by Y5: ~$565K — that's your reinvestment runway for marketing, hiring, or product expansion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Sensitivity to watch: dropping conversion to 1% would push break-even to Y3 and cap Y5 net at ~$140K. Raising to 5% pushes Y5 net to ~$1M.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• ID.me is the dominant cost — 70% of total costs in Y4-Y5. Negotiating volume pricing (typical at 100K+/yr) directly improves margin.</t>
+    <t xml:space="preserve">• Y1-Y2 show losses: ID.me verification + initial Render costs + Y2 pen-test ($5K) exceed early subscription revenue at 1K-10K users.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Y3 is the new break-even year (~$4K positive) under your moderate ramp + 3% conversion. Y4-Y5 deliver the bulk of the cumulative net.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Cumulative net by Y5: ~$375K — your reinvestment runway. (Down from ~$565K pre-Phase-4 once payment fees + pen-test were added.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Sensitivity to watch: dropping conversion to 1% would deepen losses through Y3 and push Y5 net into the red on slow/moderate ramps. Raising to 5% pushes Y5 net to ~$850K.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ID.me remains the dominant cost (~75% of Y4-Y5 total). Volume pricing (typical at 100K+ verifications/yr) directly improves margin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Payment processing (app store + Stripe) now broken out — applies the Assumptions blended rate (~10% at default 30/20/50 mix) to gross revenue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• External pen-test costs ramp from $5K (Y1) to $20K (Y5) following the cybersecurity attack-surface schedule in Assumptions row 50.</t>
   </si>
   <si>
     <t xml:space="preserve">Sensitivity — Year-5 net income at different conversion + growth</t>
@@ -680,6 +758,9 @@
   </si>
   <si>
     <t xml:space="preserve">• The 'Aggressive ramp + 1%' cell can be negative — that's the danger zone: scaling fast on free users without conversion is the worst combination.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Updated to include payment-processing fees (gross revenue × blended rate) and Y5 pen-test cost — see Assumptions rows 46 + 50. Numbers are slightly lower than the previous version because of the ~10% fee drag.</t>
   </si>
 </sst>
 </file>
@@ -694,7 +775,7 @@
     <numFmt numFmtId="168" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0&quot; months&quot;"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -853,10 +934,63 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF5F5E5A"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -954,24 +1088,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -983,7 +1121,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -991,11 +1129,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1003,15 +1141,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1019,7 +1157,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1027,11 +1165,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1055,35 +1193,67 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1091,7 +1261,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1099,11 +1269,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1111,19 +1281,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1131,7 +1309,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1394,143 +1580,143 @@
   <dimension ref="B2:C25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
+    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="6"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+      <c r="C18" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="8"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="8"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="8"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="8"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="8"/>
+      <c r="C25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1560,442 +1746,637 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>50000</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>200000</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>500000</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="20" t="n">
         <f aca="false">B7</f>
         <v>1000</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <f aca="false">C7-B7</f>
         <v>9000</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <f aca="false">D7-C7</f>
         <v>40000</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">E7-D7</f>
         <v>150000</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="20" t="n">
         <f aca="false">F7-E7</f>
         <v>300000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>0.03</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="19" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="23" t="n">
         <f aca="false">B12*12</f>
         <v>60</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="19" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="19" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="H21" s="25" t="s">
+      <c r="H21" s="26" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="H22" s="26" t="s">
+      <c r="H22" s="27" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="22" t="n">
         <v>180</v>
       </c>
-      <c r="H23" s="26" t="s">
+      <c r="H23" s="27" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="22" t="n">
         <v>450</v>
       </c>
-      <c r="H24" s="26" t="s">
+      <c r="H24" s="27" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="22" t="n">
         <v>1000</v>
       </c>
-      <c r="H25" s="26" t="s">
+      <c r="H25" s="27" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="22" t="n">
         <v>2500</v>
       </c>
-      <c r="H26" s="26" t="s">
+      <c r="H26" s="27" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="22" t="n">
         <v>5000</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="H27" s="27" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="21" t="n">
+      <c r="B28" s="22" t="n">
         <v>25000</v>
       </c>
-      <c r="H28" s="26" t="s">
+      <c r="H28" s="27" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="21" t="n">
+      <c r="B29" s="22" t="n">
         <v>250000</v>
       </c>
-      <c r="H29" s="26" t="s">
+      <c r="H29" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="s">
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="21" t="n">
+      <c r="B32" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="H32" s="26" t="s">
+      <c r="H32" s="27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="21" t="n">
+      <c r="B33" s="22" t="n">
         <v>500</v>
       </c>
-      <c r="H33" s="26" t="s">
+      <c r="H33" s="27" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="21" t="n">
+      <c r="B34" s="22" t="n">
         <v>300</v>
       </c>
-      <c r="H34" s="26" t="s">
+      <c r="H34" s="27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="21" t="n">
+      <c r="B35" s="22" t="n">
         <v>200</v>
       </c>
-      <c r="H35" s="26" t="s">
+      <c r="H35" s="27" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B36" s="21" t="n">
+      <c r="B36" s="22" t="n">
         <v>500</v>
       </c>
-      <c r="H36" s="26" t="s">
+      <c r="H36" s="28" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="27" t="n">
+      <c r="B37" s="29" t="n">
         <f aca="false">SUM(B32:B36)</f>
         <v>1550</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="25" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="30" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="28" t="s">
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="28" t="s">
+      <c r="B40" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H40" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="28" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28" t="s">
+      <c r="B41" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" s="33" t="n">
+        <f aca="false">1-B40-B41</f>
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H43" s="28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H45" s="28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="35" t="n">
+        <f aca="false">B40*B43+B41*B44+B42*B45</f>
+        <v>0.1</v>
+      </c>
+      <c r="H46" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D50" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E50" s="36" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F50" s="36" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H50" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="37"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="37"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" s="37"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="37"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" s="37"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="37"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="37"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" s="37"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
+      <c r="H57" s="37"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="37"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="37"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
+      <c r="H60" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A43:H43"/>
+  <mergeCells count="8">
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A60:H60"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2015,245 +2396,245 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>90</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="A4" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="31" t="n">
+      <c r="A6" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="40" t="n">
         <f aca="false">1000*'1. Assumptions'!B17</f>
         <v>1000</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="41" t="n">
         <f aca="false">'1. Assumptions'!B16</f>
         <v>1.5</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">B7*C7</f>
         <v>1500</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">D7/12</f>
         <v>125</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="42" t="n">
         <f aca="false">D7/(B7*'1. Assumptions'!B11*'1. Assumptions'!B12)</f>
         <v>10</v>
       </c>
-      <c r="G7" s="26" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="31" t="n">
+      <c r="G7" s="27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="40" t="n">
         <f aca="false">10000*'1. Assumptions'!B17</f>
         <v>10000</v>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="41" t="n">
         <f aca="false">'1. Assumptions'!B16</f>
         <v>1.5</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">B8*C8</f>
         <v>15000</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">D8/12</f>
         <v>1250</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="42" t="n">
         <f aca="false">D8/(B8*'1. Assumptions'!B11*'1. Assumptions'!B12)</f>
         <v>10</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="31" t="n">
+      <c r="G8" s="27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="40" t="n">
         <f aca="false">100000*'1. Assumptions'!B17</f>
         <v>100000</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="41" t="n">
         <f aca="false">'1. Assumptions'!B16</f>
         <v>1.5</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">B9*C9</f>
         <v>150000</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="23" t="n">
         <f aca="false">D9/12</f>
         <v>12500</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="42" t="n">
         <f aca="false">D9/(B9*'1. Assumptions'!B11*'1. Assumptions'!B12)</f>
         <v>10</v>
       </c>
-      <c r="G9" s="26" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="31" t="n">
+      <c r="G9" s="27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" s="40" t="n">
         <f aca="false">500000*'1. Assumptions'!B17</f>
         <v>500000</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="41" t="n">
         <f aca="false">'1. Assumptions'!B16</f>
         <v>1.5</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">B10*C10</f>
         <v>750000</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <f aca="false">D10/12</f>
         <v>62500</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="42" t="n">
         <f aca="false">D10/(B10*'1. Assumptions'!B11*'1. Assumptions'!B12)</f>
         <v>10</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="31" t="n">
+      <c r="G10" s="27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="40" t="n">
         <f aca="false">1000000*'1. Assumptions'!B17</f>
         <v>1000000</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="41" t="n">
         <f aca="false">'1. Assumptions'!B16</f>
         <v>1.5</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">B11*C11</f>
         <v>1500000</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="23" t="n">
         <f aca="false">D11/12</f>
         <v>125000</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="42" t="n">
         <f aca="false">D11/(B11*'1. Assumptions'!B11*'1. Assumptions'!B12)</f>
         <v>10</v>
       </c>
-      <c r="G11" s="26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>108</v>
+      <c r="G11" s="27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="A14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="A15" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="A16" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="A17" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2277,348 +2658,353 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="38" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-    </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="29" t="s">
+      <c r="B6" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="H6" s="38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="43" t="n">
         <f aca="false">'1. Assumptions'!B22</f>
         <v>50</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="43" t="n">
         <f aca="false">'1. Assumptions'!B37/12</f>
         <v>129.166666666667</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">B7+C7</f>
         <v>179.166666666667</v>
       </c>
-      <c r="E7" s="35" t="n">
-        <f aca="false">ROUNDUP(D7/'1. Assumptions'!B12, 0)</f>
-        <v>36</v>
-      </c>
-      <c r="F7" s="35" t="n">
+      <c r="E7" s="44" t="n">
+        <f aca="false">ROUNDUP(D7/('1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)),0)</f>
+        <v>40</v>
+      </c>
+      <c r="F7" s="44" t="n">
         <f aca="false">1000*'1. Assumptions'!B11</f>
         <v>30</v>
       </c>
-      <c r="G7" s="35" t="n">
+      <c r="G7" s="44" t="n">
         <f aca="false">F7-E7</f>
-        <v>-6</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <f aca="false">F7*'1. Assumptions'!B12-D7</f>
-        <v>-29.1666666666667</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="34" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <f aca="false">F7*'1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)-D7</f>
+        <v>-44.1666666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="43" t="n">
         <f aca="false">'1. Assumptions'!B23</f>
         <v>180</v>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C8" s="43" t="n">
         <f aca="false">'1. Assumptions'!B37/12</f>
         <v>129.166666666667</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">B8+C8</f>
         <v>309.166666666667</v>
       </c>
-      <c r="E8" s="35" t="n">
-        <f aca="false">ROUNDUP(D8/'1. Assumptions'!B12, 0)</f>
-        <v>62</v>
-      </c>
-      <c r="F8" s="35" t="n">
+      <c r="E8" s="44" t="n">
+        <f aca="false">ROUNDUP(D8/('1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)),0)</f>
+        <v>69</v>
+      </c>
+      <c r="F8" s="44" t="n">
         <f aca="false">10000*'1. Assumptions'!B11</f>
         <v>300</v>
       </c>
-      <c r="G8" s="35" t="n">
+      <c r="G8" s="44" t="n">
         <f aca="false">F8-E8</f>
-        <v>238</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <f aca="false">F8*'1. Assumptions'!B12-D8</f>
-        <v>1190.83333333333</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="34" t="n">
+        <v>231</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <f aca="false">F8*'1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)-D8</f>
+        <v>1040.83333333333</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="43" t="n">
         <f aca="false">'1. Assumptions'!B24</f>
         <v>450</v>
       </c>
-      <c r="C9" s="34" t="n">
+      <c r="C9" s="43" t="n">
         <f aca="false">'1. Assumptions'!B37/12</f>
         <v>129.166666666667</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">B9+C9</f>
         <v>579.166666666667</v>
       </c>
-      <c r="E9" s="35" t="n">
-        <f aca="false">ROUNDUP(D9/'1. Assumptions'!B12, 0)</f>
-        <v>116</v>
-      </c>
-      <c r="F9" s="35" t="n">
+      <c r="E9" s="44" t="n">
+        <f aca="false">ROUNDUP(D9/('1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)),0)</f>
+        <v>129</v>
+      </c>
+      <c r="F9" s="44" t="n">
         <f aca="false">50000*'1. Assumptions'!B11</f>
         <v>1500</v>
       </c>
-      <c r="G9" s="35" t="n">
+      <c r="G9" s="44" t="n">
         <f aca="false">F9-E9</f>
-        <v>1384</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <f aca="false">F9*'1. Assumptions'!B12-D9</f>
-        <v>6920.83333333333</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="34" t="n">
+        <v>1371</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <f aca="false">F9*'1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)-D9</f>
+        <v>6170.83333333333</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="43" t="n">
         <f aca="false">'1. Assumptions'!B24</f>
         <v>450</v>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C10" s="43" t="n">
         <f aca="false">'1. Assumptions'!B37/12</f>
         <v>129.166666666667</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">B10+C10</f>
         <v>579.166666666667</v>
       </c>
-      <c r="E10" s="35" t="n">
-        <f aca="false">ROUNDUP(D10/'1. Assumptions'!B12, 0)</f>
-        <v>116</v>
-      </c>
-      <c r="F10" s="35" t="n">
+      <c r="E10" s="44" t="n">
+        <f aca="false">ROUNDUP(D10/('1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)),0)</f>
+        <v>129</v>
+      </c>
+      <c r="F10" s="44" t="n">
         <f aca="false">100000*'1. Assumptions'!B11</f>
         <v>3000</v>
       </c>
-      <c r="G10" s="35" t="n">
+      <c r="G10" s="44" t="n">
         <f aca="false">F10-E10</f>
-        <v>2884</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <f aca="false">F10*'1. Assumptions'!B12-D10</f>
-        <v>14420.8333333333</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="34" t="n">
+        <v>2871</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <f aca="false">F10*'1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)-D10</f>
+        <v>12920.8333333333</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" s="43" t="n">
         <f aca="false">'1. Assumptions'!B25</f>
         <v>1000</v>
       </c>
-      <c r="C11" s="34" t="n">
+      <c r="C11" s="43" t="n">
         <f aca="false">'1. Assumptions'!B37/12</f>
         <v>129.166666666667</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">B11+C11</f>
         <v>1129.16666666667</v>
       </c>
-      <c r="E11" s="35" t="n">
-        <f aca="false">ROUNDUP(D11/'1. Assumptions'!B12, 0)</f>
-        <v>226</v>
-      </c>
-      <c r="F11" s="35" t="n">
+      <c r="E11" s="44" t="n">
+        <f aca="false">ROUNDUP(D11/('1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)),0)</f>
+        <v>251</v>
+      </c>
+      <c r="F11" s="44" t="n">
         <f aca="false">200000*'1. Assumptions'!B11</f>
         <v>6000</v>
       </c>
-      <c r="G11" s="35" t="n">
+      <c r="G11" s="44" t="n">
         <f aca="false">F11-E11</f>
-        <v>5774</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <f aca="false">F11*'1. Assumptions'!B12-D11</f>
-        <v>28870.8333333333</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="34" t="n">
+        <v>5749</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <f aca="false">F11*'1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)-D11</f>
+        <v>25870.8333333333</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="43" t="n">
         <f aca="false">'1. Assumptions'!B26</f>
         <v>2500</v>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C12" s="43" t="n">
         <f aca="false">'1. Assumptions'!B37/12</f>
         <v>129.166666666667</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">B12+C12</f>
         <v>2629.16666666667</v>
       </c>
-      <c r="E12" s="35" t="n">
-        <f aca="false">ROUNDUP(D12/'1. Assumptions'!B12, 0)</f>
-        <v>526</v>
-      </c>
-      <c r="F12" s="35" t="n">
+      <c r="E12" s="44" t="n">
+        <f aca="false">ROUNDUP(D12/('1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)),0)</f>
+        <v>585</v>
+      </c>
+      <c r="F12" s="44" t="n">
         <f aca="false">500000*'1. Assumptions'!B11</f>
         <v>15000</v>
       </c>
-      <c r="G12" s="35" t="n">
+      <c r="G12" s="44" t="n">
         <f aca="false">F12-E12</f>
-        <v>14474</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <f aca="false">F12*'1. Assumptions'!B12-D12</f>
-        <v>72370.8333333333</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="34" t="n">
+        <v>14415</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <f aca="false">F12*'1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)-D12</f>
+        <v>64870.8333333333</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="43" t="n">
         <f aca="false">'1. Assumptions'!B27</f>
         <v>5000</v>
       </c>
-      <c r="C13" s="34" t="n">
+      <c r="C13" s="43" t="n">
         <f aca="false">'1. Assumptions'!B37/12</f>
         <v>129.166666666667</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <f aca="false">B13+C13</f>
         <v>5129.16666666667</v>
       </c>
-      <c r="E13" s="35" t="n">
-        <f aca="false">ROUNDUP(D13/'1. Assumptions'!B12, 0)</f>
-        <v>1026</v>
-      </c>
-      <c r="F13" s="35" t="n">
+      <c r="E13" s="44" t="n">
+        <f aca="false">ROUNDUP(D13/('1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)),0)</f>
+        <v>1140</v>
+      </c>
+      <c r="F13" s="44" t="n">
         <f aca="false">1000000*'1. Assumptions'!B11</f>
         <v>30000</v>
       </c>
-      <c r="G13" s="35" t="n">
+      <c r="G13" s="44" t="n">
         <f aca="false">F13-E13</f>
-        <v>28974</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <f aca="false">F13*'1. Assumptions'!B12-D13</f>
-        <v>144870.833333333</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>125</v>
+        <v>28860</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <f aca="false">F13*'1. Assumptions'!$B$12*(1-'1. Assumptions'!$B$46)-D13</f>
+        <v>129870.833333333</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="A17" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="A18" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="A19" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="A20" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="45" t="s">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2645,287 +3031,287 @@
   <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>131</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="A4" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" s="29" t="s">
+      <c r="A6" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>137</v>
+      <c r="F6" s="38" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" s="37" t="n">
+      <c r="A7" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" s="46" t="n">
         <v>50</v>
       </c>
-      <c r="F7" s="38" t="s">
-        <v>141</v>
+      <c r="F7" s="47" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="36" t="s">
+      <c r="A8" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="46" t="n">
+        <v>180</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="B9" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="46" t="n">
+        <v>450</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" s="46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="37" t="n">
-        <v>450</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" s="37" t="n">
-        <v>450</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="E11" s="37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="37" t="n">
+      <c r="E12" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="F12" s="38" t="s">
-        <v>159</v>
+      <c r="F12" s="47" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="D13" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="E13" s="37" t="n">
+      <c r="A13" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="46" t="n">
         <v>5000</v>
       </c>
-      <c r="F13" s="38" t="s">
-        <v>163</v>
+      <c r="F13" s="47" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="E14" s="37" t="n">
+      <c r="A14" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="46" t="n">
         <v>25000</v>
       </c>
-      <c r="F14" s="38" t="s">
-        <v>168</v>
+      <c r="F14" s="47" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>172</v>
-      </c>
-      <c r="E15" s="37" t="n">
+      <c r="A15" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="46" t="n">
         <v>250000</v>
       </c>
-      <c r="F15" s="38" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>175</v>
+      <c r="F15" s="47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
+      <c r="A20" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="A21" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="A22" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
+      <c r="A23" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2950,434 +3336,498 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>181</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="49" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A6" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="40" t="n">
         <f aca="false">'1. Assumptions'!B7</f>
         <v>1000</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="40" t="n">
         <f aca="false">'1. Assumptions'!C7</f>
         <v>10000</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">'1. Assumptions'!D7</f>
         <v>50000</v>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="E7" s="40" t="n">
         <f aca="false">'1. Assumptions'!E7</f>
         <v>200000</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="40" t="n">
         <f aca="false">'1. Assumptions'!F7</f>
         <v>500000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="40" t="n">
         <f aca="false">'1. Assumptions'!B8</f>
         <v>1000</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="40" t="n">
         <f aca="false">'1. Assumptions'!C8</f>
         <v>9000</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="40" t="n">
         <f aca="false">'1. Assumptions'!D8</f>
         <v>40000</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="40" t="n">
         <f aca="false">'1. Assumptions'!E8</f>
         <v>150000</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="40" t="n">
         <f aca="false">'1. Assumptions'!F8</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B9" s="35" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="44" t="n">
         <f aca="false">ROUND(B7*'1. Assumptions'!$B$11,0)</f>
         <v>30</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="44" t="n">
         <f aca="false">ROUND(C7*'1. Assumptions'!$B$11,0)</f>
         <v>300</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="44" t="n">
         <f aca="false">ROUND(D7*'1. Assumptions'!$B$11,0)</f>
         <v>1500</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="44" t="n">
         <f aca="false">ROUND(E7*'1. Assumptions'!$B$11,0)</f>
         <v>6000</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="44" t="n">
         <f aca="false">ROUND(F7*'1. Assumptions'!$B$11,0)</f>
         <v>15000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="B12" s="22" t="n">
+      <c r="A11" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <f aca="false">B9*'1. Assumptions'!$B$13</f>
         <v>1800</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <f aca="false">C9*'1. Assumptions'!$B$13</f>
         <v>18000</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">D9*'1. Assumptions'!$B$13</f>
         <v>90000</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <f aca="false">E9*'1. Assumptions'!$B$13</f>
         <v>360000</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <f aca="false">F9*'1. Assumptions'!$B$13</f>
         <v>900000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="B13" s="40" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="50" t="n">
         <f aca="false">B12</f>
         <v>1800</v>
       </c>
-      <c r="C13" s="40" t="n">
+      <c r="C13" s="50" t="n">
         <f aca="false">C12</f>
         <v>18000</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="50" t="n">
         <f aca="false">D12</f>
         <v>90000</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="50" t="n">
         <f aca="false">E12</f>
         <v>360000</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="50" t="n">
         <f aca="false">F12</f>
         <v>900000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="B16" s="22" t="n">
+      <c r="A15" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="23" t="n">
         <f aca="false">B8*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17</f>
         <v>1500</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <f aca="false">C8*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17</f>
         <v>13500</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <f aca="false">D8*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17</f>
         <v>60000</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="23" t="n">
         <f aca="false">E8*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17</f>
         <v>225000</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="23" t="n">
         <f aca="false">F8*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17</f>
         <v>450000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="B17" s="22" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <f aca="false">IF(B7&lt;=1000,'1. Assumptions'!$B$22,IF(B7&lt;=10000,'1. Assumptions'!$B$23,IF(B7&lt;=50000,'1. Assumptions'!$B$24,IF(B7&lt;=200000,'1. Assumptions'!$B$25,IF(B7&lt;=500000,'1. Assumptions'!$B$26,IF(B7&lt;=1000000,'1. Assumptions'!$B$27,'1. Assumptions'!$B$28))))))*12</f>
         <v>600</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="23" t="n">
         <f aca="false">IF(C7&lt;=1000,'1. Assumptions'!$B$22,IF(C7&lt;=10000,'1. Assumptions'!$B$23,IF(C7&lt;=50000,'1. Assumptions'!$B$24,IF(C7&lt;=200000,'1. Assumptions'!$B$25,IF(C7&lt;=500000,'1. Assumptions'!$B$26,IF(C7&lt;=1000000,'1. Assumptions'!$B$27,'1. Assumptions'!$B$28))))))*12</f>
         <v>2160</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="23" t="n">
         <f aca="false">IF(D7&lt;=1000,'1. Assumptions'!$B$22,IF(D7&lt;=10000,'1. Assumptions'!$B$23,IF(D7&lt;=50000,'1. Assumptions'!$B$24,IF(D7&lt;=200000,'1. Assumptions'!$B$25,IF(D7&lt;=500000,'1. Assumptions'!$B$26,IF(D7&lt;=1000000,'1. Assumptions'!$B$27,'1. Assumptions'!$B$28))))))*12</f>
         <v>5400</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="23" t="n">
         <f aca="false">IF(E7&lt;=1000,'1. Assumptions'!$B$22,IF(E7&lt;=10000,'1. Assumptions'!$B$23,IF(E7&lt;=50000,'1. Assumptions'!$B$24,IF(E7&lt;=200000,'1. Assumptions'!$B$25,IF(E7&lt;=500000,'1. Assumptions'!$B$26,IF(E7&lt;=1000000,'1. Assumptions'!$B$27,'1. Assumptions'!$B$28))))))*12</f>
         <v>12000</v>
       </c>
-      <c r="F17" s="22" t="n">
+      <c r="F17" s="23" t="n">
         <f aca="false">IF(F7&lt;=1000,'1. Assumptions'!$B$22,IF(F7&lt;=10000,'1. Assumptions'!$B$23,IF(F7&lt;=50000,'1. Assumptions'!$B$24,IF(F7&lt;=200000,'1. Assumptions'!$B$25,IF(F7&lt;=500000,'1. Assumptions'!$B$26,IF(F7&lt;=1000000,'1. Assumptions'!$B$27,'1. Assumptions'!$B$28))))))*12</f>
         <v>30000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="34" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="43" t="n">
         <f aca="false">'1. Assumptions'!$B$37</f>
         <v>1550</v>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C18" s="43" t="n">
         <f aca="false">'1. Assumptions'!$B$37</f>
         <v>1550</v>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D18" s="43" t="n">
         <f aca="false">'1. Assumptions'!$B$37</f>
         <v>1550</v>
       </c>
-      <c r="E18" s="34" t="n">
+      <c r="E18" s="43" t="n">
         <f aca="false">'1. Assumptions'!$B$37</f>
         <v>1550</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F18" s="43" t="n">
         <f aca="false">'1. Assumptions'!$B$37</f>
         <v>1550</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="40" t="n">
-        <f aca="false">SUM(B16:B18)</f>
-        <v>3650</v>
-      </c>
-      <c r="C19" s="40" t="n">
-        <f aca="false">SUM(C16:C18)</f>
-        <v>17210</v>
-      </c>
-      <c r="D19" s="40" t="n">
-        <f aca="false">SUM(D16:D18)</f>
-        <v>66950</v>
-      </c>
-      <c r="E19" s="40" t="n">
-        <f aca="false">SUM(E16:E18)</f>
-        <v>238550</v>
-      </c>
-      <c r="F19" s="40" t="n">
-        <f aca="false">SUM(F16:F18)</f>
-        <v>481550</v>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="51" t="n">
+        <f aca="false">B13*'1. Assumptions'!$B$46</f>
+        <v>180</v>
+      </c>
+      <c r="C19" s="51" t="n">
+        <f aca="false">C13*'1. Assumptions'!$B$46</f>
+        <v>1800</v>
+      </c>
+      <c r="D19" s="51" t="n">
+        <f aca="false">D13*'1. Assumptions'!$B$46</f>
+        <v>9000</v>
+      </c>
+      <c r="E19" s="51" t="n">
+        <f aca="false">E13*'1. Assumptions'!$B$46</f>
+        <v>36000</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <f aca="false">F13*'1. Assumptions'!$B$46</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" s="51" t="n">
+        <f aca="false">'1. Assumptions'!B50</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="51" t="n">
+        <f aca="false">'1. Assumptions'!C50</f>
+        <v>5000</v>
+      </c>
+      <c r="D20" s="51" t="n">
+        <f aca="false">'1. Assumptions'!D50</f>
+        <v>10000</v>
+      </c>
+      <c r="E20" s="51" t="n">
+        <f aca="false">'1. Assumptions'!E50</f>
+        <v>15000</v>
+      </c>
+      <c r="F20" s="51" t="n">
+        <f aca="false">'1. Assumptions'!F50</f>
+        <v>20000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="41" t="n">
-        <f aca="false">B13-B19</f>
-        <v>-1850</v>
-      </c>
-      <c r="C22" s="41" t="n">
-        <f aca="false">C13-C19</f>
-        <v>790</v>
-      </c>
-      <c r="D22" s="41" t="n">
-        <f aca="false">D13-D19</f>
-        <v>23050</v>
-      </c>
-      <c r="E22" s="41" t="n">
-        <f aca="false">E13-E19</f>
-        <v>121450</v>
-      </c>
-      <c r="F22" s="41" t="n">
-        <f aca="false">F13-F19</f>
-        <v>418450</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="B23" s="42" t="n">
-        <f aca="false">B22</f>
-        <v>-1850</v>
-      </c>
-      <c r="C23" s="42" t="n">
-        <f aca="false">B23+C22</f>
-        <v>-1060</v>
-      </c>
-      <c r="D23" s="42" t="n">
-        <f aca="false">C23+D22</f>
-        <v>21990</v>
-      </c>
-      <c r="E23" s="42" t="n">
-        <f aca="false">D23+E22</f>
-        <v>143440</v>
-      </c>
-      <c r="F23" s="42" t="n">
-        <f aca="false">E23+F22</f>
-        <v>561890</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B24" s="43" t="n">
-        <f aca="false">IFERROR(B22/B13,0)</f>
-        <v>-1.02777777777778</v>
-      </c>
-      <c r="C24" s="43" t="n">
-        <f aca="false">IFERROR(C22/C13,0)</f>
-        <v>0.0438888888888889</v>
-      </c>
-      <c r="D24" s="43" t="n">
-        <f aca="false">IFERROR(D22/D13,0)</f>
-        <v>0.256111111111111</v>
-      </c>
-      <c r="E24" s="43" t="n">
-        <f aca="false">IFERROR(E22/E13,0)</f>
-        <v>0.337361111111111</v>
-      </c>
-      <c r="F24" s="43" t="n">
-        <f aca="false">IFERROR(F22/F13,0)</f>
-        <v>0.464944444444444</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>196</v>
+      <c r="A21" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="50" t="n">
+        <f aca="false">SUM(B16:B20)</f>
+        <v>3830</v>
+      </c>
+      <c r="C21" s="50" t="n">
+        <f aca="false">SUM(C16:C20)</f>
+        <v>24010</v>
+      </c>
+      <c r="D21" s="50" t="n">
+        <f aca="false">SUM(D16:D20)</f>
+        <v>85950</v>
+      </c>
+      <c r="E21" s="50" t="n">
+        <f aca="false">SUM(E16:E20)</f>
+        <v>289550</v>
+      </c>
+      <c r="F21" s="50" t="n">
+        <f aca="false">SUM(F16:F20)</f>
+        <v>591550</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B24" s="52" t="n">
+        <f aca="false">B13-B21</f>
+        <v>-2030</v>
+      </c>
+      <c r="C24" s="52" t="n">
+        <f aca="false">C13-C21</f>
+        <v>-6010</v>
+      </c>
+      <c r="D24" s="52" t="n">
+        <f aca="false">D13-D21</f>
+        <v>4050</v>
+      </c>
+      <c r="E24" s="52" t="n">
+        <f aca="false">E13-E21</f>
+        <v>70450</v>
+      </c>
+      <c r="F24" s="52" t="n">
+        <f aca="false">F13-F21</f>
+        <v>308450</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B25" s="53" t="n">
+        <f aca="false">B24</f>
+        <v>-2030</v>
+      </c>
+      <c r="C25" s="53" t="n">
+        <f aca="false">B25+C24</f>
+        <v>-8040</v>
+      </c>
+      <c r="D25" s="53" t="n">
+        <f aca="false">C25+D24</f>
+        <v>-3990</v>
+      </c>
+      <c r="E25" s="53" t="n">
+        <f aca="false">D25+E24</f>
+        <v>66460</v>
+      </c>
+      <c r="F25" s="53" t="n">
+        <f aca="false">E25+F24</f>
+        <v>374910</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="54" t="n">
+        <f aca="false">IFERROR(B24/B13,0)</f>
+        <v>-1.12777777777778</v>
+      </c>
+      <c r="C26" s="54" t="n">
+        <f aca="false">IFERROR(C24/C13,0)</f>
+        <v>-0.333888888888889</v>
+      </c>
+      <c r="D26" s="54" t="n">
+        <f aca="false">IFERROR(D24/D13,0)</f>
+        <v>0.045</v>
+      </c>
+      <c r="E26" s="54" t="n">
+        <f aca="false">IFERROR(E24/E13,0)</f>
+        <v>0.195694444444444</v>
+      </c>
+      <c r="F26" s="54" t="n">
+        <f aca="false">IFERROR(F24/F13,0)</f>
+        <v>0.342722222222222</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="A28" s="56" t="s">
+        <v>220</v>
+      </c>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
+      <c r="A29" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+      <c r="A30" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
+      <c r="A31" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="45" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="45" t="s">
+        <v>227</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3402,152 +3852,157 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>203</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="A4" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="22" t="n">
-        <f aca="false">250000*0.01*'1. Assumptions'!$B$13-(150000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+12000+'1. Assumptions'!$B$37)</f>
-        <v>-88550</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <f aca="false">250000*0.03*'1. Assumptions'!$B$13-(150000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+12000+'1. Assumptions'!$B$37)</f>
-        <v>211450</v>
-      </c>
-      <c r="D7" s="22" t="n">
-        <f aca="false">250000*0.05*'1. Assumptions'!$B$13-(150000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+12000+'1. Assumptions'!$B$37)</f>
-        <v>511450</v>
-      </c>
-      <c r="E7" s="22" t="n">
-        <f aca="false">250000*0.1*'1. Assumptions'!$B$13-(150000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+12000+'1. Assumptions'!$B$37)</f>
-        <v>1261450</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="B8" s="22" t="n">
-        <f aca="false">500000*0.01*'1. Assumptions'!$B$13-(300000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+30000+'1. Assumptions'!$B$37)</f>
-        <v>-181550</v>
-      </c>
-      <c r="C8" s="45" t="n">
-        <f aca="false">500000*0.03*'1. Assumptions'!$B$13-(300000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+30000+'1. Assumptions'!$B$37)</f>
-        <v>418450</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <f aca="false">500000*0.05*'1. Assumptions'!$B$13-(300000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+30000+'1. Assumptions'!$B$37)</f>
-        <v>1018450</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <f aca="false">500000*0.1*'1. Assumptions'!$B$13-(300000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+30000+'1. Assumptions'!$B$37)</f>
-        <v>2518450</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="22" t="n">
-        <f aca="false">1000000*0.01*'1. Assumptions'!$B$13-(500000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+60000+'1. Assumptions'!$B$37)</f>
-        <v>-211550</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <f aca="false">1000000*0.03*'1. Assumptions'!$B$13-(500000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+60000+'1. Assumptions'!$B$37)</f>
-        <v>988450</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <f aca="false">1000000*0.05*'1. Assumptions'!$B$13-(500000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+60000+'1. Assumptions'!$B$37)</f>
-        <v>2188450</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <f aca="false">1000000*0.1*'1. Assumptions'!$B$13-(500000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+60000+'1. Assumptions'!$B$37)</f>
-        <v>5188450</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>213</v>
+      <c r="A6" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <f aca="false">(250000*0.01*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(150000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+12000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>-123550</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <f aca="false">(250000*0.03*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(150000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+12000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>146450</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <f aca="false">(250000*0.05*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(150000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+12000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>416450</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <f aca="false">(250000*0.1*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(150000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+12000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>1091450</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <f aca="false">(500000*0.01*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(300000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+30000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>-231550</v>
+      </c>
+      <c r="C8" s="58" t="n">
+        <f aca="false">(500000*0.03*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(300000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+30000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>308450</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <f aca="false">(500000*0.05*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(300000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+30000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>848450</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <f aca="false">(500000*0.1*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(300000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+30000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>2198450</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9" s="23" t="n">
+        <f aca="false">(1000000*0.01*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(500000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+60000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>-291550</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <f aca="false">(1000000*0.03*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(500000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+60000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>788450</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <f aca="false">(1000000*0.05*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(500000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+60000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>1868450</v>
+      </c>
+      <c r="E9" s="23" t="n">
+        <f aca="false">(1000000*0.1*'1. Assumptions'!$B$13)*(1-'1. Assumptions'!$B$46)-(500000*'1. Assumptions'!$B$16*'1. Assumptions'!$B$17+60000+'1. Assumptions'!$B$37+'1. Assumptions'!$F$50)</f>
+        <v>4568450</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="A12" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="A13" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="A14" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="A15" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="45" t="s">
+        <v>244</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/docs/civicview_financial_model.xlsx
+++ b/docs/civicview_financial_model.xlsx
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -30,8 +30,9 @@
     <numFmt numFmtId="168" formatCode="0.0&quot; months&quot;"/>
     <numFmt numFmtId="169" formatCode="$#,##0.00"/>
     <numFmt numFmtId="170" formatCode="$#,##0"/>
+    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -286,6 +287,17 @@
     <font>
       <color rgb="001F4E79"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF5F5E5A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -335,7 +347,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -677,6 +689,11 @@
     <xf numFmtId="166" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf numFmtId="171" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1140,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="59" min="1" max="1"/>
@@ -1891,7 +1908,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="59" t="inlineStr">
         <is>
           <t>Google Workspace Business Starter (annual)</t>
         </is>
@@ -1900,14 +1917,14 @@
         <f>8.4*12</f>
         <v/>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="59" t="inlineStr">
         <is>
           <t>$8.40/mo x 12 = $100.80/yr. Custom domain email + Drive/Docs for the founder.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="59" t="inlineStr">
         <is>
           <t>Vote Smart API license — OPTIONAL toggle (1 = include, 0 = exclude)</t>
         </is>
@@ -1915,14 +1932,14 @@
       <c r="B64" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="59" t="inlineStr">
         <is>
           <t>Set to 1 to include the Vote Smart license cost in the model. Default 0 (off).</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="59" t="inlineStr">
         <is>
           <t>Vote Smart Public-Facing Platform License (annual list price)</t>
         </is>
@@ -1930,14 +1947,14 @@
       <c r="B65" s="98" t="n">
         <v>4850</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="59" t="inlineStr">
         <is>
           <t>votesmart.org Public-Facing Platform License, 1-year subscription. Quoted June 2026.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="59" t="inlineStr">
         <is>
           <t>Vote Smart applied (toggle x license)</t>
         </is>
@@ -1946,9 +1963,107 @@
         <f>B64*B65</f>
         <v/>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="59" t="inlineStr">
         <is>
           <t>Flows into 'Total other recurring' only when the toggle above = 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="95" t="inlineStr">
+        <is>
+          <t>Crowdfunding (Indiegogo) — one-time raise (added 2026-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gross campaign goal / raise</t>
+        </is>
+      </c>
+      <c r="B69" s="117" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H69" s="118" t="inlineStr">
+        <is>
+          <t>Indiegogo Flexible-funding goal. Blue = edit me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Indiegogo platform fee rate</t>
+        </is>
+      </c>
+      <c r="B70" s="119" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H70" s="118" t="inlineStr">
+        <is>
+          <t>Indiegogo flat 5% platform fee (Flexible or Fixed) as of 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Payment processing rate (effective)</t>
+        </is>
+      </c>
+      <c r="B71" s="119" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H71" s="118" t="inlineStr">
+        <is>
+          <t>~2.9% + $0.30 per contribution; ~3% effective at typical gift sizes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Combined Indiegogo fee rate</t>
+        </is>
+      </c>
+      <c r="B72" s="120">
+        <f>B70+B71</f>
+        <v/>
+      </c>
+      <c r="H72" s="118" t="inlineStr">
+        <is>
+          <t>Auto. ~8% all-in — vs GoFundMe's 0% platform / optional-donor-tip model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Net proceeds after fees</t>
+        </is>
+      </c>
+      <c r="B73" s="121">
+        <f>B69*(1-B72)</f>
+        <v/>
+      </c>
+      <c r="H73" s="118" t="inlineStr">
+        <is>
+          <t>What actually lands in the business account. ~$23,000 on a funded $25K raise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>• One-time inflow. Deliberately NOT in 'Total other recurring' (B37) or the 5-Year P&amp;L — those model ongoing operations only. The raise funds the Year-2 buffer; see indiegogo_draft.md.</t>
         </is>
       </c>
     </row>
